--- a/artfynd/A 25030-2026 artfynd.xlsx
+++ b/artfynd/A 25030-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832980</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832757</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832652</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832648</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832631</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832655</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832643</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832646</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832666</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832640</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832664</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832665</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2214,6 +2284,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832756</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2321,6 +2396,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832635</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832749</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2535,6 +2620,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832762</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2642,6 +2732,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832629</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2749,6 +2844,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832636</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2856,6 +2956,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832638</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2963,6 +3068,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832654</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3085,6 +3195,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832657</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3207,6 +3322,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832647</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3334,6 +3454,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832633</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3446,6 +3571,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832639</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3553,6 +3683,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832753</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3660,6 +3795,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832755</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3767,6 +3907,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832743</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3874,6 +4019,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832661</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3990,6 +4140,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832650</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4106,6 +4261,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832656</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4222,6 +4382,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832659</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4338,6 +4503,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832662</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4454,6 +4624,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832663</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4570,6 +4745,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832758</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4687,6 +4867,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832759</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4799,6 +4984,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832760</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4906,6 +5096,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832763</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5022,6 +5217,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832764</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5129,6 +5329,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832637</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5236,6 +5441,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832649</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5343,6 +5553,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832628</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5450,6 +5665,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832642</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5557,6 +5777,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832645</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5664,6 +5889,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832651</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5771,6 +6001,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832653</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5878,6 +6113,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832748</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5985,6 +6225,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832751</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6092,6 +6337,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832752</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6199,6 +6449,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832634</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6306,6 +6561,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832750</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6413,6 +6673,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832626</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6535,6 +6800,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832622</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6642,6 +6912,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832728</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6749,6 +7024,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832729</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6856,6 +7136,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832624</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6963,6 +7248,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832733</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7070,6 +7360,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832630</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7182,6 +7477,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832732</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7294,6 +7594,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832731</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7410,6 +7715,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832621</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7531,6 +7841,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832726</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7647,6 +7962,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832734</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7763,6 +8083,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832735</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7879,6 +8204,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832737</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8000,6 +8330,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832738</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8116,6 +8451,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832739</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8232,6 +8572,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832740</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8348,6 +8693,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832741</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8464,6 +8814,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832742</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8571,6 +8926,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832736</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8678,6 +9038,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832623</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8785,6 +9150,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832730</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8892,8 +9262,89 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832625</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>